--- a/files/九龙-何文田-瑜一第IC期.xlsx
+++ b/files/九龙-何文田-瑜一第IC期.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -146,8 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +220,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,13 +238,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -10543,115 +10581,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑜一第IC期 - 5A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>70 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>67 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1213呎 (4+房)
 招标单位
@@ -10659,7 +10697,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1207呎 (4+房)
 招标单位
@@ -10667,15 +10705,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1213呎 (4+房)
 招标单位
@@ -10683,693 +10721,693 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1208呎 (4+房)
-$4,828万
+$4828万
 $39,967/呎
 (26年-07月)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,989万
+$2989万
 $32,000/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,603万
+$1603万
 $27,833/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$3,030万
+$3030万
 $33,522/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$3,022万
+$3022万
 $32,353/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,875万
+$1875万
 $32,554/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,971万
+$2971万
 $32,866/呎
 (23年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,861万
+$2861万
 $30,635/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,845万
+$1845万
 $32,039/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,913万
+$2913万
 $32,221/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,904万
+$2904万
 $31,096/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,765万
+$1765万
 $30,634/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,856万
+$2856万
 $31,588/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,849万
+$2849万
 $30,500/呎
 (26年-07月)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,806万
+$1806万
 $31,362/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,833万
+$2833万
 $31,337/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,858万
+$2858万
 $30,605/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,783万
+$1783万
 $30,954/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,712万
+$2712万
 $30,000/呎
 (26年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,836万
+$2836万
 $30,361/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,755万
+$1755万
 $30,474/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,763万
+$2763万
 $30,569/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,836万
+$2836万
 $30,361/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,755万
+$1755万
 $30,474/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,716万
+$2716万
 $30,048/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,801万
+$2801万
 $29,986/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,698万
+$1698万
 $29,472/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,558万
+$2558万
 $28,300/呎
 (26年-02月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,597万
+$2597万
 $27,800/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,649万
+$1649万
 $28,634/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,590万
+$2590万
 $28,656/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,756万
+$2756万
 $29,504/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,676万
+$1676万
 $29,095/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,584万
+$2584万
 $28,589/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,729万
+$2729万
 $29,214/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,647万
+$1647万
 $28,595/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,581万
+$2581万
 $28,554/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,676万
+$2676万
 $28,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,595万
+$1595万
 $27,697/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,499万
+$2499万
 $27,644/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,620万
+$2620万
 $28,050/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,549万
+$1549万
 $26,892/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,426万
+$2426万
 $26,838/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,569万
+$2569万
 $27,500/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,519万
+$1519万
 $26,365/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,338万
+$2338万
 $25,864/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,518万
+$2518万
 $26,961/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,489万
+$1489万
 $25,847/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,332万
+$2332万
 $25,796/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,385万
+$2385万
 $25,531/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,325万
+$1325万
 $23,007/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,286万
+$2286万
 $25,290/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,279万
+$2279万
 $24,400/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,407万
+$1407万
 $24,421/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,203万
+$2203万
 $24,372/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,310万
+$2310万
 $24,731/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,399万
+$1399万
 $24,282/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,139万
+$2139万
 $23,662/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,299万
+$2299万
 $24,611/呎
 (23年-04月)</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,338万
+$1338万
 $23,223/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,113万
+$2113万
 $23,372/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 934呎 (3房)
-$2,174万
+$2174万
 $23,274/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 576呎 (2房)
-$1,372万
+$1372万
 $23,812/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
-$2,045万
+$2045万
 $22,621/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 891呎 (3房)
-$2,617万
+$2617万
 $29,374/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 533呎 (2房)
-$1,538万
+$1538万
 $28,855/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
-$2,435万
+$2435万
 $28,280/呎
 (已售)</t>
         </is>
@@ -11377,7 +11415,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -11390,1441 +11428,1441 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑜一第IC期 - 5B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>144 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>144 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$2,377万
+$2377万
 $36,240/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,620万
+$1620万
 $35,146/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,395万
+$1395万
 $29,998/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,631万
+$1631万
 $34,992/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,792万
+$1792万
 $34,598/呎
 (23年-04月)</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,497万
+$1497万
 $28,738/呎
 (25年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$2,149万
+$2149万
 $32,755/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,275万
+$1275万
 $27,655/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,421万
+$1421万
 $30,563/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,273万
+$1273万
 $27,317/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,648万
+$1648万
 $31,811/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,375万
+$1375万
 $26,397/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$2,166万
+$2166万
 $33,021/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,300万
+$1300万
 $28,208/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,260万
+$1260万
 $27,101/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,254万
+$1254万
 $26,912/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,623万
+$1623万
 $31,340/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,355万
+$1355万
 $26,001/呎
 (25年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,814万
+$1814万
 $27,654/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,238万
+$1238万
 $26,844/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,363万
+$1363万
 $29,315/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,445万
+$1445万
 $31,015/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,599万
+$1599万
 $30,876/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,335万
+$1335万
 $25,617/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$2,103万
+$2103万
 $32,053/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,262万
+$1262万
 $27,381/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,359万
+$1359万
 $29,227/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,375万
+$1375万
 $29,517/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,454万
+$1454万
 $28,065/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,321万
+$1321万
 $25,355/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$2,071万
+$2071万
 $31,570/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,201万
+$1201万
 $26,055/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,339万
+$1339万
 $28,794/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,403万
+$1403万
 $30,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,545万
+$1545万
 $29,831/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,312万
+$1312万
 $25,174/呎
 (25年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,747万
+$1747万
 $26,631/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,194万
+$1194万
 $25,900/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,331万
+$1331万
 $28,622/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,371万
+$1371万
 $29,417/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,564万
+$1564万
 $30,200/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,519万
+$1519万
 $29,146/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,733万
+$1733万
 $26,421/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,187万
+$1187万
 $25,747/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,191万
+$1191万
 $25,608/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,386万
+$1386万
 $29,748/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,417万
+$1417万
 $27,362/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,448万
+$1448万
 $27,784/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$2,024万
+$2024万
 $30,850/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,181万
+$1181万
 $25,616/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,363万
+$1363万
 $29,311/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,379万
+$1379万
 $29,601/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,523万
+$1523万
 $29,408/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,478万
+$1478万
 $28,369/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,720万
+$1720万
 $26,223/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,181万
+$1181万
 $25,616/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,363万
+$1363万
 $29,311/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,379万
+$1379万
 $29,601/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,478万
+$1478万
 $28,542/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,457万
+$1457万
 $27,957/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,994万
+$1994万
 $30,393/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,349万
+$1349万
 $29,263/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,343万
+$1343万
 $28,877/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,359万
+$1359万
 $29,163/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,484万
+$1484万
 $28,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,440万
+$1440万
 $27,646/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,973万
+$1973万
 $30,080/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,281万
+$1281万
 $27,788/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,148万
+$1148万
 $24,688/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,334万
+$1334万
 $28,630/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,449万
+$1449万
 $27,973/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,408万
+$1408万
 $27,030/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,650万
+$1650万
 $25,146/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,321万
+$1321万
 $28,654/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,293万
+$1293万
 $27,803/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,329万
+$1329万
 $28,517/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,443万
+$1443万
 $27,859/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,404万
+$1404万
 $26,949/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,641万
+$1641万
 $25,013/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,316万
+$1316万
 $28,544/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,310万
+$1310万
 $28,171/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,324万
+$1324万
 $28,402/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,437万
+$1437万
 $27,751/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,400万
+$1400万
 $26,869/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,876万
+$1876万
 $28,598/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,266万
+$1266万
 $27,460/呎
 (23年-04月)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,305万
+$1305万
 $28,058/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,318万
+$1318万
 $28,288/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,383万
+$1383万
 $26,695/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,374万
+$1374万
 $26,368/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,624万
+$1624万
 $24,751/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,305万
+$1305万
 $28,316/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,130万
+$1130万
 $24,297/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,313万
+$1313万
 $28,177/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,308万
+$1308万
 $25,260/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,342万
+$1342万
 $25,766/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,905万
+$1905万
 $29,041/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,300万
+$1300万
 $28,202/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,294万
+$1294万
 $27,834/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,124万
+$1124万
 $24,126/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,420万
+$1420万
 $27,419/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,349万
+$1349万
 $25,890/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,601万
+$1601万
 $24,405/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,118万
+$1118万
 $24,244/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,294万
+$1294万
 $27,834/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,308万
+$1308万
 $28,064/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,303万
+$1303万
 $25,162/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,349万
+$1349万
 $25,890/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,890万
+$1890万
 $28,811/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,238万
+$1238万
 $26,857/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,239万
+$1239万
 $26,639/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,289万
+$1289万
 $27,661/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,409万
+$1409万
 $27,202/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,339万
+$1339万
 $25,709/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,882万
+$1882万
 $28,696/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,277万
+$1277万
 $27,696/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,274万
+$1274万
 $27,401/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,104万
+$1104万
 $23,683/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,403万
+$1403万
 $27,093/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,327万
+$1327万
 $25,466/呎
 (23年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,576万
+$1576万
 $24,020/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,228万
+$1228万
 $26,643/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,269万
+$1269万
 $27,291/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,279万
+$1279万
 $27,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,398万
+$1398万
 $26,984/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,308万
+$1308万
 $25,101/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,868万
+$1868万
 $28,468/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,089万
+$1089万
 $23,617/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,264万
+$1264万
 $27,182/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,274万
+$1274万
 $27,331/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,369万
+$1369万
 $26,419/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,297万
+$1297万
 $24,897/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 656呎 (3房)
-$1,860万
+$1860万
 $28,354/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
-$1,261万
+$1261万
 $27,364/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
-$1,259万
+$1259万
 $27,074/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
-$1,269万
+$1269万
 $27,223/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 518呎 (2房)
-$1,387万
+$1387万
 $26,772/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>F | 521呎 (2房)
-$1,284万
+$1284万
 $24,652/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 619呎 (3房)
-$2,022万
+$2022万
 $32,665/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 423呎 (2房)
-$1,132万
+$1132万
 $26,754/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 427呎 (2房)
-$1,309万
+$1309万
 $30,666/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 428呎 (2房)
-$1,317万
+$1317万
 $30,769/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 481呎 (2房)
-$1,503万
+$1503万
 $31,237/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>F | 483呎 (2房)
-$1,496万
+$1496万
 $30,978/呎
 (已售)</t>
         </is>
@@ -12832,7 +12870,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
